--- a/yash-data/questions.xlsx
+++ b/yash-data/questions.xlsx
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -490,7 +490,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -564,12 +564,12 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
@@ -635,148 +635,148 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Percentages</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>In which sentence is the word "effect" used incorrectly?</t>
+          <t>A price rises from ₹800 to ₹1,000. What is the percentage increase?</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The medicine took effect within an hour.</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Lack of sleep can effect your concentration.</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The new policy will effect major changes in hiring.</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The ban comes into effect from Monday.</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>"Affect" is the verb for influencing something. "Effect" as a verb means to bring about, as in the first option.</t>
+          <t>Increase 200 on 800: 200/800 × 100 = 25%.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Choose the correct option: Each of the students ___ the assignment on time.</t>
+          <t>₹1,200 is divided between A and B in the ratio 3 : 5. What is B's share?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>are submitting</t>
+          <t>₹750</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>have submitted</t>
+          <t>₹800</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>has submitted</t>
+          <t>₹450</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>were submitted</t>
+          <t>₹720</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>"Each" is singular, so it takes "has".</t>
+          <t>B gets 5/8 of 1,200 = ₹750.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Averages</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hardly had he reached the station ___ the train left.</t>
+          <t>The average of 5 numbers is 24. If the number 20 is removed, what is the average of the other four?</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>while</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>then</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -787,102 +787,102 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>"Hardly ... when" is the fixed pairing. "No sooner" takes "than".</t>
+          <t>Total 120. Without 20 it is 100, and 100/4 = 25.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Profit, Loss and Discount</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Fill in the blank: He is senior ___ me by two years.</t>
+          <t>An article bought for ₹400 is sold for ₹460. What is the profit percentage?</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Senior, junior, superior and inferior take "to", not "than".</t>
+          <t>Profit 60 on cost 400: 60/400 × 100 = 15%.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Time and Work</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version of the underlined part: [If I was you], I would accept the offer.</t>
+          <t>A can finish a job in 10 days and B in 15 days. Working together, how long do they take?</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>If I were you</t>
+          <t>6 days</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If I am you</t>
+          <t>7.5 days</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>If I had been you</t>
+          <t>5 days</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>If I was you</t>
+          <t>12.5 days</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -893,261 +893,263 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Hypothetical present uses the subjunctive "were".</t>
+          <t>Per day: 1/10 + 1/15 = 1/6, so 6 days.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Time, Speed and Distance</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>She is ___ honest woman.</t>
+          <t>A car travels at 72 km/h. How many metres does it cover in 15 seconds?</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>1080 m</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>no article</t>
+          <t>360 m</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>250 m</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>300 m</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>"Honest" starts with a vowel sound (silent h).</t>
+          <t>72 km/h = 72 × 5/18 = 20 m/s. 20 × 15 = 300 m.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Simple and Compound Interest</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>___ Ganga is a sacred river.</t>
+          <t>What is the simple interest on ₹5,000 at 8% per year for 3 years?</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>₹1,298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>₹1,200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>₹1,500</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>₹1,000</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Names of rivers take "the".</t>
+          <t>SI = P × R × T / 100 = 5000 × 8 × 3 / 100 = ₹1,200.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Number System</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>He plays ___ guitar beautifully.</t>
+          <t>What is the LCM of 12, 18 and 24?</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>no article</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Musical instruments take "the" after "play".</t>
+          <t>12 = 2²×3, 18 = 2×3², 24 = 2³×3. LCM = 2³ × 3² = 72.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Which noun cannot be preceded by the indefinite article "a"?</t>
+          <t>Units sold by a shop:
+Jan 120 · Feb 150 · Mar 90 · Apr 140
+What is the average monthly sale?</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>advice</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>pen</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Advice is uncountable; say "a piece of advice".</t>
+          <t>Total 500 over 4 months: 500/4 = 125.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Probability and P&amp;C</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>He is ___ European and holds ___ MBA.</t>
+          <t>A die is rolled once. What is the probability of getting a number greater than 4?</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>an, an</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>an, a</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>a, a</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>a, an</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1158,420 +1160,422 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>"European" starts with a "y" sound; "MBA" starts with an "em" sound.</t>
+          <t>Only 5 and 6: 2 of 6 = 1/3.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Number and Alphabet Series</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>A car covers 240 km in 4 hours. By how much must its speed increase to cover the same distance in 3 hours?</t>
+          <t>3, 6, 12, 24, ?</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20 km/h</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15 km/h</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25 km/h</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30 km/h</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>240/4 = 60 and 240/3 = 80, so 20 km/h more.</t>
+          <t>Each term is double the previous one.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Coding and Decoding</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Two trains, 120 m and 180 m long, run in opposite directions at 40 km/h and 50 km/h. How long do they take to cross each other?</t>
+          <t>If CAT is coded as DBU, how is DOG coded?</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18 s</t>
+          <t>EPH</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15 s</t>
+          <t>FQI</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12 s</t>
+          <t>DPH</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10 s</t>
+          <t>EPG</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Relative speed 90 km/h = 25 m/s. Distance 300 m. 300/25 = 12 s.</t>
+          <t>Each letter moves one step forward: D→E, O→P, G→H.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Blood Relations</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>A train 150 m long passes a pole in 10 seconds. What is its speed?</t>
+          <t>Pointing to a boy, Rina says, "He is the son of my mother's only son." How is the boy related to Rina?</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45 km/h</t>
+          <t>Nephew</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50 km/h</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54 km/h</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60 km/h</t>
+          <t>Cousin</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>150/10 = 15 m/s = 15 × 18/5 = 54 km/h.</t>
+          <t>Her mother's only son is Rina's brother. His son is her nephew.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>In how many ways can the letters of the word LEADER be arranged?</t>
+          <t>Ravi walks 4 km north, turns right and walks 3 km. How far is he from the start?</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>4 km</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>5 km</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>7 km</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1 km</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6!/2! = 360 (E repeats).</t>
+          <t>He ends 4 km north and 3 km east: √(4² + 3²) = 5 km.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Seating Arrangements</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>A committee of 3 is chosen from 5 men and 4 women. In how many ways can it include at least one woman?</t>
+          <t>Five friends sit in a row facing north. A is at the left end, C is in the middle, B is to the immediate right of A, and D is not at an end. Who is at the right end?</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>C(9,3) − C(5,3) = 84 − 10 = 74.</t>
+          <t>From the left: A, B, C, D, E.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Logical Puzzles</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>In how many ways can 4 books, chosen from 6 different books, be arranged on a shelf?</t>
+          <t>P, Q, R and S live on floors 1 to 4 of a building, one on each floor. P lives above Q but below R. S lives on floor 1. Who lives on floor 4?</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>P(6,4) = 6 × 5 × 4 × 3 = 360.</t>
+          <t>S is on 1, so Q, P, R take floors 2, 3, 4 in that order.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Syllogisms</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>In what ratio must rice at ₹40/kg be mixed with rice at ₹55/kg to get a mixture worth ₹45/kg?</t>
+          <t>Statements: All roses are flowers. All flowers are plants.
+Conclusion I: All roses are plants.
+Conclusion II: All plants are roses.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Alligation: (55 − 45) : (45 − 40) = 10 : 5 = 2 : 1.</t>
+          <t>Roses sit inside flowers, which sit inside plants, so I follows. Plants can include much more than roses, so II does not.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Ranking and Order</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>A 40-litre mixture has milk and water in the ratio 3 : 1. How much milk must be added to make the ratio 4 : 1?</t>
+          <t>In a row of 30 students, Amit is 12th from the left. What is his position from the right?</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10 litres</t>
+          <t>19th</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5 litres</t>
+          <t>20th</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8 litres</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12 litres</t>
+          <t>18th</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1582,162 +1586,160 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Milk 30, water 10. For 4 : 1 milk must be 40, so add 10 litres.</t>
+          <t>30 − 12 + 1 = 19.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Data Sufficiency</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Two dice are thrown. What is the probability that the sum is 8?</t>
+          <t>What is the value of x?
+(I) x + y = 10
+(II) x − y = 4</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>Only one of the statements alone is enough</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>Both statements together are needed, but neither alone</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7/36</t>
+          <t>Cannot be answered even with both statements</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5/36</t>
+          <t>Each statement alone is enough</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>(2,6),(3,5),(4,4),(5,3),(6,2): 5 outcomes of 36.</t>
+          <t>Neither alone fixes x. Together: adding gives 2x = 14, so x = 7.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Calendars and Clocks</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>A bag has 4 red and 6 blue balls. Two are drawn at random. What is the probability both are red?</t>
+          <t>What is the angle between the hour and minute hands at 3:30?</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>90°</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>75°</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>80°</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>60°</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>C(4,2)/C(10,2) = 6/45 = 2/15.</t>
+          <t>Hour hand: 3 × 30 + 30 × 0.5 = 105°. Minute hand: 180°. Difference 75°.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Subject-Verb Agreement</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5, 11, 23, 47, 95, ?</t>
+          <t>The list of items ___ on the table.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>have been</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>were</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>B</t>
@@ -1745,113 +1747,105 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Each term = previous × 2 + 1.</t>
+          <t>The subject is "list", which is singular.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Tenses</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2, 5, 10, 17, 26, ?</t>
+          <t>By the time we reached the cinema, the film ___.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>had started</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>has started</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>will start</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>starts</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>n² + 1 for n = 1, 2, 3, ...</t>
+          <t>An action finished before another past action takes the past perfect.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Error Spotting</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4, 9, 25, 49, 121, ?</t>
+          <t>Find the part with the error: She do not / like coffee / in the morning.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>She do not</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>like coffee</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>in the morning</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>No error</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -1859,385 +1853,372 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Squares of primes: 2, 3, 5, 7, 11, 13.</t>
+          <t>"She" takes "does not".</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Sentence Correction</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7, 10, 16, 25, 37, ?</t>
+          <t>Choose the correct sentence.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>He is more taller than his brother.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>He is most tall than his brother.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>He is taller than his brother.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>He is tallest than his brother.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Differences 3, 6, 9, 12, 15.</t>
+          <t>"Taller" is already a comparative; do not add "more".</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1, 2, 6, 24, 120, ?</t>
+          <t>Passage: Bees visit flowers to collect nectar. While doing so, pollen sticks to their bodies and is carried to other flowers, helping plants produce seeds. Without bees, many crops would give much smaller harvests.
+What is the main idea of the passage?</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>Flowers make nectar to attract all insects equally.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>Crops grow only where bees live.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>Bees play an important role in helping plants produce seeds.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>Bees make honey from pollen.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Factorials: 6! = 720, which is not listed.</t>
+          <t>Every sentence builds towards bees helping plants reproduce.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Para Jumbles</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>What is the value of x?
-(I) 3x + 2 = 11
-(II) x² = 9</t>
+          <t>Arrange the sentences in order:
+P: She bought a ticket and boarded the bus.
+Q: Meena wanted to visit her grandmother.
+R: After a two-hour ride, she reached the village.
+S: So she went to the bus stand early in the morning.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>SQPR</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>QPSR</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>QSRP</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>QSPR</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>I gives x = 3. II gives x = 3 or −3.</t>
+          <t>Reason (Q), going to the stand (S), boarding (P), arriving (R).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Fill in the Blanks</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Is the integer n odd?
-(I) n + 3 is even.
-(II) 2n is even.</t>
+          <t>The medicine had an immediate ___ on the patient's fever.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>affect</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>defect</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>infect</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>effect</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>I alone: n is odd. II is true for every integer.</t>
+          <t>"Effect" is the noun meaning result. "Affect" is usually a verb.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Synonyms and Antonyms</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>What is Ram's age?
-(I) Ram is 5 years older than Shyam.
-(II) The sum of their ages is 35.</t>
+          <t>Choose the word closest in meaning to ABUNDANT.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Scarce</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Tiny</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Plentiful</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Together: R − S = 5 and R + S = 35, so R = 20.</t>
+          <t>Abundant means existing in large amounts.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Articles and Prepositions</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>What is the area of a square?
-(I) Its perimeter is 20 cm.
-(II) Its diagonal is 5√2 cm.</t>
+          <t>She has been living in Pune ___ 2019.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>since</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>at</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>for</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>on</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Either one gives side = 5 cm.</t>
+          <t>"Since" goes with a starting point in time; "for" goes with a length of time.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D1R</t>
+          <t>T1R</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Critical Reasoning</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>What is the speed of the train?
-(I) The train is 200 m long.
-(II) It passes a man walking in the same direction in 20 seconds.</t>
+          <t>Argument: "Our town should build a new library because the current one is always crowded." Which is an assumption in this argument?</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Libraries are more important than schools.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>The current library has too many books.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>A new library would reduce the crowding.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>People in the town do not read books.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2248,632 +2229,634 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>The man's speed is unknown, so even both together are not enough.</t>
+          <t>The argument only works if a new library actually eases the crowding.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Percentages</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>In which sentence is the word "eminent" used incorrectly?</t>
+          <t>A town's population rises by 10% in one year and falls by 10% the next. It is now 9,900. What was it at the start?</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>The storm clouds signalled that danger was eminent.</t>
+          <t>10,100</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Several eminent jurists signed the letter.</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>An eminent scientist chaired the panel.</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>She is eminent in the field of genetics.</t>
+          <t>9,801</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Danger that is about to happen is "imminent". "Eminent" means distinguished.</t>
+          <t>Net factor 1.1 × 0.9 = 0.99. 9,900 / 0.99 = 10,000.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version of the underlined part: Not only the manager but also the employees [was responsible] for the delay.</t>
+          <t>The ratio of A's age to B's age is 4 : 5. In 8 years it will be 6 : 7. What is A's present age?</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>has been responsible</t>
+          <t>12 years</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>was responsible</t>
+          <t>16 years</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>were responsible</t>
+          <t>20 years</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>is responsible</t>
+          <t>24 years</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>With "not only ... but also", the verb agrees with the nearer subject, "employees".</t>
+          <t>(4x + 8)/(5x + 8) = 6/7 gives 28x + 56 = 30x + 48, so x = 4 and A = 16.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Averages</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>No sooner had she left the house ___ it began to rain.</t>
+          <t>The average of 11 results is 50. The average of the first six is 49 and of the last six is 52. What is the sixth result?</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>than</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>that</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>then</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>"No sooner ... than" is the fixed pairing.</t>
+          <t>The sixth is counted twice: 6×49 + 6×52 − 11×50 = 294 + 312 − 550 = 56.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Profit, Loss and Discount</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version: [Being a rainy day, the match was cancelled.]</t>
+          <t>A shopkeeper marks goods 40% above cost and gives a 15% discount. What is the profit percentage?</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>As being a rainy day, the match was cancelled.</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>It being a rainy day, the match was cancelled.</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Being a rainy day, the match was cancelled.</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Being rainy, the day cancelled the match.</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>The original says the match was a rainy day. "It being" makes a correct absolute phrase.</t>
+          <t>1.40 × 0.85 = 1.19, so 19% profit.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Time and Work</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version of the underlined part: She likes [swimming, to cycle and running].</t>
+          <t>A and B can do a job in 12 days, B and C in 15 days, and C and A in 20 days. How long will A alone take?</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>swimming, cycling and running</t>
+          <t>60 days</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>swim, cycle and running</t>
+          <t>24 days</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>swimming, to cycle and running</t>
+          <t>40 days</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>to swim, cycling and to run</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Items in a list must be parallel.</t>
+          <t>Adding the pairs: 2(A+B+C) = 1/12 + 1/15 + 1/20 = 1/5, so A+B+C = 1/10. A = 1/10 − 1/15 = 1/30.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Time, Speed and Distance</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Which group of words can ALL be preceded by "an"?</t>
+          <t>A boat goes 30 km downstream in 2 hours and comes back in 3 hours. What is its speed in still water?</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>hour, honour, MBA</t>
+          <t>2.5 km/h</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>one-day, heir, apple</t>
+          <t>12.5 km/h</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>honest, European, umbrella</t>
+          <t>13 km/h</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>hour, university, MBA</t>
+          <t>12 km/h</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>University, European and one-day start with consonant sounds (y, y, w).</t>
+          <t>Downstream 15, upstream 10. Boat = (15 + 10)/2 = 12.5 km/h.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Simple and Compound Interest</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>___ Times of India is ___ English daily.</t>
+          <t>The difference between compound and simple interest on a sum for 2 years at 10% per year is ₹50. What is the sum?</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The, an</t>
+          <t>₹2,500</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>A, an</t>
+          <t>₹4,000</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>No article, an</t>
+          <t>₹10,000</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>The, a</t>
+          <t>₹5,000</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Newspaper names take "the"; "English" starts with a vowel sound.</t>
+          <t>For 2 years, CI − SI = P × (R/100)² = P × 0.01 = 50, so P = 5,000.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Number System</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>He was ___ first to arrive and ___ last to leave.</t>
+          <t>What is the remainder when 2³¹ is divided by 5?</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>no article, no article</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>the, the</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>the, a</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>a, the</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Ordinals like first and last take "the".</t>
+          <t>Powers of 2 leave remainders 2, 4, 3, 1 and repeat every 4. 31 = 4×7 + 3, so the remainder is 3.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Mount Everest is ___ highest peak in ___ Himalayas.</t>
+          <t>Monthly spending of a family (₹ thousand):
+Rent 15 · Food 12 · Travel 6 · Others 7
+If rent rises by 20% and the rest stays the same, about what share of the new total is rent?</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>no article, the</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>the, the</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>the, no article</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>a, the</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Superlatives and mountain ranges take "the"; single peaks do not.</t>
+          <t>New rent 18, new total 43. 18/43 ≈ 41.9%.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Probability and P&amp;C</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Find the part with the error: He gave me / an useful / piece of / advice.</t>
+          <t>Three cards are drawn from a pack of 52. What is the probability that all three are hearts?</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>piece of</t>
+          <t>13/850</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>advice</t>
+          <t>11/850</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>He gave me</t>
+          <t>1/64</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>an useful</t>
+          <t>1/52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>"Useful" starts with a "y" sound, so it takes "a".</t>
+          <t>C(13,3) / C(52,3) = 286 / 22100 = 11/850.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Number and Alphabet Series</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>A man rows 30 km downstream in 3 hours and 18 km upstream in 3 hours. What is the speed of the stream?</t>
+          <t>B, D, G, K, P, ?</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2 km/h</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3 km/h</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4 km/h</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1 km/h</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Downstream 10, upstream 6. Stream = (10 − 6)/2 = 2.</t>
+          <t>Positions 2, 4, 7, 11, 16 grow by 2, 3, 4, 5. Next +6 gives 22 = V.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Coding and Decoding</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Walking at 3/4 of his usual speed, a man reaches 20 minutes late. What is his usual time?</t>
+          <t>In a code, MONKEY is written as XDJMNL. How is TIGER written?</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>80 minutes</t>
+          <t>SHFDQ</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>40 minutes</t>
+          <t>UJHFS</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>60 minutes</t>
+          <t>QDFHS</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>75 minutes</t>
+          <t>QDFHT</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2884,49 +2867,49 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Time becomes 4/3 of usual. The extra 1/3 is 20 minutes, so usual time is 60.</t>
+          <t>Reverse the word (YEKNOM) and move each letter one step back. TIGER → REGIT → QDFHS.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Blood Relations</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>In how many arrangements of BANANA are the two N's not together?</t>
+          <t>P + Q means P is the father of Q, P − Q means P is the wife of Q, and P × Q means P is the brother of Q. What does A − B + C × D tell you about A and D?</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>A is D's aunt</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>A is D's sister</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>A is D's mother</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>A is D's grandmother</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2937,598 +2920,586 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Total 6!/(3!2!) = 60. N's together: 5!/3! = 20. 60 − 20 = 40.</t>
+          <t>A is B's wife, B is C's father, and C is D's brother. So D is also B's child, and A is D's mother.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>6 boys and 4 girls stand in a row so that no two girls are together. How many arrangements are possible?</t>
+          <t>A man walks 5 km south, turns left and walks 3 km, then turns left again and walks 9 km. Where is he now from the start?</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>151200</t>
+          <t>4 km north</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>604800</t>
+          <t>7 km north-east</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>86400</t>
+          <t>5 km north-east</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>302400</t>
+          <t>5 km south-east</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Arrange boys: 6! = 720. Choose 4 of 7 gaps in order: 7×6×5×4 = 840. 720 × 840 = 604800.</t>
+          <t>He ends 4 km north and 3 km east of the start: √(4² + 3²) = 5 km, north-east.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Seating Arrangements</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>How many arrangements of the letters of DAUGHTER keep the vowels together?</t>
+          <t>Six people A to F sit around a round table facing the centre. A is opposite D. B is to the immediate right of A. C is opposite B. E is not next to D. Who is to the immediate left of D?</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Treat A, U, E as one unit: 6! × 3! = 720 × 6 = 4320.</t>
+          <t>Place A, then B on A's right and C opposite B. The two seats left are next to A and next to D; E cannot sit by D, so F does, on D's left.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Logical Puzzles</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>60 litres of a mixture has milk and water in the ratio 2 : 1. How much water must be added to make the ratio 1 : 1?</t>
+          <t>Five boxes P, Q, R, S, T are stacked one on top of another. T is at the bottom and S is directly above T. R is directly above P. Q is above S but not at the top. Which box is in the middle?</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>15 litres</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10 litres</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>20 litres</t>
+          <t>P</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30 litres</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Milk 40, water 20. Water must become 40, so add 20.</t>
+          <t>From the bottom: T, S. If P were third, R fourth, Q would be on top, which is not allowed. So Q is third, P fourth, R on top.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Syllogisms</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Two vessels hold milk and water in the ratios 3 : 2 and 7 : 3. In what ratio must they be mixed to get milk and water in the ratio 2 : 1?</t>
+          <t>Statements: All cats are dogs. Some dogs are birds.
+Conclusion I: Some cats are birds.
+Conclusion II: Some birds are dogs.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1 : 2</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2 : 1</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2 : 3</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3 : 2</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Milk fractions 3/5 and 7/10, target 2/3. (7/10 − 2/3) : (2/3 − 3/5) = 1/30 : 2/30 = 1 : 2.</t>
+          <t>The birds that are dogs may not be cats, so I does not follow. "Some dogs are birds" can be reversed, so II follows.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Ranking and Order</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Two cards are drawn from a pack of 52 without replacement. What is the probability that both are kings or both are queens?</t>
+          <t>Ravi is 15th from the left and Sohan is 20th from the right in a row. When they swap places, Ravi becomes 25th from the left. How many people are in the row?</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2/169</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2/221</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1/221</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1/169</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2 × C(4,2)/C(52,2) = 12/1326 = 2/221.</t>
+          <t>Sohan's old seat is 25th from the left and 20th from the right: 25 + 20 − 1 = 44.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Data Sufficiency</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>An urn has 4 red and 3 green balls. Three are drawn one by one without replacement. What is the probability that the colours alternate?</t>
+          <t>Is x an integer?
+(I) 2x is an integer.
+(II) x² is an integer.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>Only one of the statements alone is enough</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>Both statements together are needed, but neither alone</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>Cannot be answered even with both statements</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>12/35</t>
+          <t>Each statement alone is enough</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>RGR = 36/210, GRG = 24/210. Total 60/210 = 2/7.</t>
+          <t>I fails for x = 0.5 and II fails for x = √2. Together x = k/2 with k²/4 a whole number, so k is even and x is an integer.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Calendars and Clocks</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>A and B try a problem independently, with chances 1/2 and 1/3 of solving it. What is the probability that the problem gets solved?</t>
+          <t>What day of the week was 15 August 1947?</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1 − (1/2 × 2/3) = 1 − 1/3 = 2/3.</t>
+          <t>Odd days: 1600 years → 0, next 300 years → 1, 1901–1946 → 1, 1 Jan to 15 Aug 1947 → 3. Total 5 odd days = Friday.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Subject-Verb Agreement</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1, 2, 6, 15, 31, ?</t>
+          <t>Bread and butter ___ my usual breakfast.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>were</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>is</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>have been</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Differences are squares: 1, 4, 9, 16, 25.</t>
+          <t>"Bread and butter" is one dish, so it takes a singular verb.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Tenses</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>3, 4, 12, 39, 103, ?</t>
+          <t>She ___ in this company for ten years by next March.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>had worked</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>will be working</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>will have been working</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>has been working</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Differences are cubes: 1, 8, 27, 64, 125.</t>
+          <t>An action continuing up to a future point takes the future perfect continuous.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Error Spotting</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2, 3, 10, 15, 26, 35, ?</t>
+          <t>Find the part with the error: Scarcely had I reached the station / than the train / left the platform.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>Scarcely had I reached the station</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>than the train</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>left the platform</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>No error</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>n² + 1 and n² − 1 alternate.</t>
+          <t>"Scarcely" pairs with "when", not "than".</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Sentence Correction</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2, 3, 8, 27, 112, ?</t>
+          <t>Choose the best sentence.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>The reason why he failed is because he did not study.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>The reason he failed is because of he did not study.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>Because he did not study is the reason he failed.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>The reason he failed is that he did not study.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
           <t>D</t>
@@ -3536,163 +3507,160 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>× 1 + 1, × 2 + 2, × 3 + 3, × 4 + 4, × 5 + 5.</t>
+          <t>"The reason ... is because" repeats the idea. Use "the reason ... is that".</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>6, 12, 21, 33, 48, ?</t>
+          <t>Passage: Remote work has cut commuting time for millions. Yet surveys show many remote workers feel less connected to their teams, and some companies now ask staff to come in two or three days a week. Managers say casual conversations in the office often spark new ideas.
+Which statement can be inferred?</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>Remote work has increased commuting time.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>Some companies believe in-person contact helps produce new ideas.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>Remote workers are less productive than office workers.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>All companies have ended remote work.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Differences 6, 9, 12, 15, 18 give 66, which is not listed.</t>
+          <t>Companies calling staff back, and managers praising office conversations, point to this belief. The other options go beyond the passage.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Para Jumbles</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Is x &gt; y?
-(I) x² &gt; y²
-(II) x − y &gt; 0</t>
+          <t>Arrange the sentences in order:
+P: As a result, many cities now plant trees along busy roads.
+Q: Trees absorb dust and some harmful gases.
+R: Air pollution is a growing problem in cities.
+S: They also lower the temperature of the streets around them.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>RSQP</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>QRSP</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>RQPS</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>RQSP</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>II alone answers yes. I fails for x = −3, y = 1.</t>
+          <t>Problem (R), first benefit (Q), second benefit (S), result (P).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Fill in the Blanks</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>What is x + y?
-(I) 2x + 3y = 12
-(II) 4x + 6y = 24</t>
+          <t>His explanation was so ___ that even the experts were confused.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>lucid</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>concise</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>convoluted</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>candid</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3703,267 +3671,261 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>II is I doubled, so there is only one equation in two unknowns.</t>
+          <t>Convoluted means complicated and hard to follow, which fits "even the experts were confused".</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Synonyms and Antonyms</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Is the positive integer n divisible by 6?
-(I) n is divisible by 12.
-(II) n is divisible by 3.</t>
+          <t>Choose the word most nearly OPPOSITE in meaning to EPHEMERAL.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Delicate</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Brief</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Fleeting</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>I alone answers yes. II fails for n = 3.</t>
+          <t>Ephemeral means lasting a very short time.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Articles and Prepositions</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>What is the ratio of A's salary to B's?
-(I) A earns 25% more than B.
-(II) B earns 20% less than A.</t>
+          <t>The thief was accused ___ theft and sent ___ jail.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>of, in</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>of, to</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>with, into</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>for, to</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Both give A : B = 5 : 4.</t>
+          <t>Accused of something; sent to jail.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>D1H</t>
+          <t>T1H</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Critical Reasoning</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>What is the two-digit number?
-(I) The sum of its digits is 9.
-(II) Reversing the digits makes it 27 larger.</t>
+          <t>Argument: "Since new traffic signals were put in, accidents at the junction have fallen by 30%. So the signals made the junction safer." Which, if true, most weakens the argument?</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Drivers say they like the new signals.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Accidents across the city rose overall.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>The signals cost less than expected.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>In the same period, the junction was closed for four months for repairs.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>II gives b − a = 3. With I: a = 3, b = 6, so 36.</t>
+          <t>If the road was closed for months, fewer accidents could be due to less traffic, not the signals.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Percentages</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>In which sentence is the word "principle" used incorrectly?</t>
+          <t>A student scores 72 out of 90. What percentage is that?</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>The principle of the school addressed the parents.</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>The basic principle of the machine is simple.</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>He refused to cheat on principle.</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>She is a woman of principle.</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>The head of a school is the "principal".</t>
+          <t>72/90 × 100 = 80%.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>The number of applicants ___ increased this year.</t>
+          <t>If A : B = 2 : 3 and B : C = 4 : 5, what is A : C?</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>have</t>
+          <t>3 : 5</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>has</t>
+          <t>8 : 15</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>2 : 5</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>were</t>
+          <t>8 : 12</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3974,49 +3936,49 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>"The number of" is singular. "A number of" is plural.</t>
+          <t>Make B equal: A : B : C = 8 : 12 : 15, so A : C = 8 : 15.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Averages</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>I look forward to ___ you.</t>
+          <t>The average age of 4 friends is 20 years. When a fifth friend joins, the average becomes 21. How old is the fifth friend?</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>meeting</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>meet</t>
+          <t>21 years</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>have met</t>
+          <t>26 years</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>24 years</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -4027,102 +3989,102 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>"Look forward to" is followed by a gerund.</t>
+          <t>New total 5 × 21 = 105, old total 80. 105 − 80 = 25.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Profit, Loss and Discount</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>She is good ___ mathematics.</t>
+          <t>A shirt marked ₹800 is sold at a 15% discount. What is the selling price?</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>₹650</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>₹685</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>with</t>
+          <t>₹680</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>₹720</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Good at a subject or skill.</t>
+          <t>15% of 800 is 120. 800 − 120 = ₹680.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Time and Work</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Choose the correct sentence.</t>
+          <t>12 workers can build a wall in 10 days. How many days will 8 workers take?</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Neither the teacher nor the students was ready.</t>
+          <t>12 days</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Neither of the teacher nor the students was ready.</t>
+          <t>18 days</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Neither the teacher or the students were ready.</t>
+          <t>13 days</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Neither the teacher nor the students were ready.</t>
+          <t>15 days</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4133,420 +4095,422 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>"Neither ... nor"; the verb agrees with the nearer subject, "students".</t>
+          <t>Total work 12 × 10 = 120 worker-days. 120 / 8 = 15.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Time, Speed and Distance</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>It was ___ unique opportunity.</t>
+          <t>A 200 m train crosses a 300 m bridge at 36 km/h. How long does it take?</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>no article</t>
+          <t>30 s</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>20 s</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>45 s</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>50 s</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>"Unique" starts with a "y" sound.</t>
+          <t>Distance 500 m. 36 km/h = 10 m/s. 500 / 10 = 50 s.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Simple and Compound Interest</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>___ sun rises in ___ east.</t>
+          <t>What is the compound interest on ₹10,000 at 10% per year for 2 years?</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>A, the</t>
+          <t>₹1,100</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>The, no article</t>
+          <t>₹2,000</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The, the</t>
+          <t>₹2,200</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>No article, the</t>
+          <t>₹2,100</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Unique objects and directions take "the".</t>
+          <t>10,000 × 1.1² = 12,100, so CI = ₹2,100.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Number System</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>He is ___ one-eyed man.</t>
+          <t>What is the HCF of 36 and 48?</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>no article</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>"One" starts with a "w" sound.</t>
+          <t>36 = 2²×3², 48 = 2⁴×3. HCF = 2² × 3 = 12.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>She went to ___ hospital to visit her friend.</t>
+          <t>Books sold by a shop:
+Mon 40 · Tue 55 · Wed 35 · Thu 70
+By what percentage did sales rise from Wednesday to Thursday?</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>no article</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>She is a visitor, not a patient, so the specific building takes "the".</t>
+          <t>From 35 to 70 is a rise of 35 on 35, which is 100%.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Probability and P&amp;C</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Which noun cannot be preceded by "a"?</t>
+          <t>In how many ways can 5 people stand in a line?</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>luggage</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>trolley</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>suitcase</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>bag</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Luggage is uncountable.</t>
+          <t>5! = 5 × 4 × 3 × 2 × 1 = 120.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Number and Alphabet Series</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>A man goes to a town at 30 km/h and returns at 20 km/h. The whole trip takes 10 hours. How far is the town?</t>
+          <t>A, C, F, J, O, ?</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>120 km</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>150 km</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>100 km</t>
+          <t>V</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>125 km</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>d/30 + d/20 = 10, so d/12 = 10 and d = 120.</t>
+          <t>Positions 1, 3, 6, 10, 15 grow by 2, 3, 4, 5. Next +6 gives 21 = U.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Coding and Decoding</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>A 200 m train crosses a 300 m platform in 25 seconds. What is its speed?</t>
+          <t>Each letter is replaced by its position in the alphabet and the numbers are added. SUN = 54. What is MOON?</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>60 km/h</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>80 km/h</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>54 km/h</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>72 km/h</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>500/25 = 20 m/s = 72 km/h.</t>
+          <t>M 13 + O 15 + O 15 + N 14 = 57.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Blood Relations</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>A cyclist covers 36 km in 2 hours 15 minutes. What is the cyclist's speed?</t>
+          <t>A is B's sister. C is B's mother. D is C's father. How is A related to D?</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>18 km/h</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>16 km/h</t>
+          <t>Granddaughter</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>15 km/h</t>
+          <t>Niece</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>14 km/h</t>
+          <t>Grandmother</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4557,427 +4521,427 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>36 / 2.25 = 16 km/h.</t>
+          <t>A is C's daughter, and C is D's child, so A is D's granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>In how many ways can the letters of APPLE be arranged?</t>
+          <t>Neha faces east, turns 90° clockwise, then turns 180°. Which way does she face now?</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>South</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>East</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>West</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5!/2! = 60.</t>
+          <t>East → 90° clockwise → south → 180° → north.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Seating Arrangements</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>12 people shake hands once with each other. How many handshakes are there?</t>
+          <t>Five people sit in a row facing north. P is at the right end, Q is to the immediate left of P, and R is at the left end. S is not next to R. Who is second from the left?</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>C(12,2) = 66.</t>
+          <t>R, _, _, Q, P. S cannot sit by R, so S is third and T is second.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Logical Puzzles</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>In how many ways can a captain and a vice-captain be chosen from a team of 11 players?</t>
+          <t>A, B, C and D are all different heights. A is taller than B. C is shorter than B. D is taller than A. Who is the shortest?</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>11 × 10 = 110 (order matters).</t>
+          <t>D &gt; A &gt; B &gt; C.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Syllogisms</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>In what ratio must water be mixed with milk costing ₹60 per litre to get a mixture worth ₹50 per litre?</t>
+          <t>Statements: All teachers are graduates. Some graduates are singers.
+Conclusion I: Some teachers are singers.
+Conclusion II: All singers are graduates.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1 : 6</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1 : 5</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1 : 4</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>5 : 1</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Water costs 0. (60 − 50) : (50 − 0) = 10 : 50 = 1 : 5 (water : milk).</t>
+          <t>The singers among graduates need not be teachers, and only some singers are known to be graduates. Neither follows.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Ranking and Order</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>20 kg of sugar at ₹30/kg is mixed with 30 kg at ₹40/kg. What is the cost of the mixture per kg?</t>
+          <t>Meera is 7th from the top and 26th from the bottom in her class. How many students are in the class?</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>₹36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>₹35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>₹38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>₹34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>(600 + 1200) / 50 = ₹36.</t>
+          <t>7 + 26 − 1 = 32.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Data Sufficiency</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>A card is drawn from a pack of 52. What is the probability that it is a heart or a king?</t>
+          <t>Is the number n divisible by 4?
+(I) n is divisible by 8.
+(II) n is even.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>Only one of the statements alone is enough</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>17/52</t>
+          <t>Both statements together are needed, but neither alone</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>Cannot be answered even with both statements</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>Each statement alone is enough</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>13 hearts + 3 other kings = 16. 16/52 = 4/13.</t>
+          <t>I alone says yes, because 8 is a multiple of 4. II fails for n = 6.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Calendars and Clocks</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Three coins are tossed. What is the probability of exactly two heads?</t>
+          <t>What is the angle between the hands of a clock at 4:20?</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>0°</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>HHT, HTH, THH: 3 of 8.</t>
+          <t>Hour hand: 4 × 30 + 20 × 0.5 = 130°. Minute hand: 120°. Difference 10°.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Subject-Verb Agreement</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1, 8, 27, 64, ?</t>
+          <t>Neither of the two answers ___ correct.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>were</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>is</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>are</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>have</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
           <t>B</t>
@@ -4985,279 +4949,266 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Cubes of 1 to 5.</t>
+          <t>"Neither of" is singular.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Tenses</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>3, 6, 18, 72, 360, ?</t>
+          <t>I ___ my homework already, so I can watch TV now.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>will finish</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>have finished</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>finish</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>had finished</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>× 2, × 3, × 4, × 5, × 6.</t>
+          <t>"Already" with a result that matters now takes the present perfect.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Error Spotting</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>120, 99, 80, 63, 48, ?</t>
+          <t>Find the part with the error: He has been working / here since / five years.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>He has been working</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>here since</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>five years</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>No error</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>n² − 1 for n = 11, 10, 9, 8, 7, 6.</t>
+          <t>A length of time takes "for": here for five years.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Sentence Correction</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2, 4, 12, 48, 240, ?</t>
+          <t>Choose the correct sentence.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>I prefer tea over than coffee.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>I prefer tea than coffee.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>I prefer tea from coffee.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>I prefer tea to coffee.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>× 2, × 3, × 4, × 5, × 6 gives 1440, which is not listed.</t>
+          <t>"Prefer" is followed by "to", not "than".</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>10, 14, 22, 38, 70, ?</t>
+          <t>Passage: The town of Riverside started a weekend market in 2020. Local farmers sell vegetables, fruit and honey directly to buyers. Prices are lower than in shops because there are no middlemen, and farmers earn more per kilo.
+According to the passage, why are prices at the market lower?</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>There are no middlemen between farmers and buyers.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>The government pays part of the price.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>The market opens only at weekends.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>The produce is of lower quality.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Differences double: 4, 8, 16, 32, 64.</t>
+          <t>The passage says so directly: "because there are no middlemen".</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Para Jumbles</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>What is the cost of one pen?
-(I) 5 pens and 3 pencils cost ₹40.
-(II) One pencil costs ₹5.</t>
+          <t>Arrange the sentences in order:
+P: Finally, he cooked them on a hot pan.
+Q: He rolled the dough into flat circles.
+R: Raju decided to make chapatis.
+S: Then he mixed the flour with water.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>RSPQ</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>RSQP</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>SRQP</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>RQSP</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -5268,428 +5219,420 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Together: 5p + 15 = 40, so p = ₹5.</t>
+          <t>Decision (R), mixing (S), rolling (Q), cooking (P).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Fill in the Blanks</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Is today Wednesday?
-(I) The day after tomorrow is Friday.
-(II) Yesterday was Tuesday.</t>
+          <t>The hikers were ___ after walking for eight hours.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>exhausted</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>energetic</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>refreshed</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Either one alone gives Wednesday.</t>
+          <t>Eight hours of walking leaves you very tired.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Synonyms and Antonyms</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>What is the value of y?
-(I) y³ = −64
-(II) y² = 16</t>
+          <t>Choose the word opposite in meaning to ANCIENT.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Antique</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Historic</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>I gives y = −4. II gives 4 or −4.</t>
+          <t>Ancient means very old; modern means new.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Articles and Prepositions</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>What is the profit percentage?
-(I) The selling price is 125% of the cost price.
-(II) The profit is ₹100.</t>
+          <t>She is fond ___ music.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>for</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>with</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>of</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>about</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>I alone gives 25%. II has no cost price.</t>
+          <t>The fixed phrase is "fond of".</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>D2R</t>
+          <t>T2R</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Critical Reasoning</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>How old is Priya?
-(I) Priya is twice as old as Neha.
-(II) Neha is 3 years younger than Ravi.</t>
+          <t>Statement: "All employees must wear ID cards inside the office." Which assumption is being made?</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>ID cards are expensive to make.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Visitors never come to the office.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Employees do not like ID cards.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>ID cards help identify who is allowed inside.</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Ravi's age is unknown, so even both are not enough.</t>
+          <t>The rule only makes sense if ID cards help check who belongs there.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Percentages</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>In which sentence is the word "disinterested" used incorrectly?</t>
+          <t>In an election between two candidates, the winner got 58% of the votes and won by 1,120 votes. How many votes were cast?</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>As a disinterested observer, she gave a fair account.</t>
+          <t>7,200</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>The students looked disinterested and kept yawning during the lecture.</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>A judge must be disinterested in the outcome of a case.</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>We need a disinterested third party to settle the dispute.</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>"Disinterested" means impartial. Bored students are "uninterested".</t>
+          <t>The margin is 58% − 42% = 16% of the votes. 1,120 / 0.16 = 7,000.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version of the underlined part: The quality of these apples [are not good].</t>
+          <t>Two numbers are in the ratio 3 : 5. If 9 is subtracted from each, the ratio becomes 12 : 23. What is the smaller number?</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>is not good</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>are not good</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>have not been good</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>were not good</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>The subject is "quality", which is singular.</t>
+          <t>(3x − 9)/(5x − 9) = 12/23 gives 69x − 207 = 60x − 108, so x = 11 and the numbers are 33 and 55.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Averages</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>He is one of those men who ___ always ready to help.</t>
+          <t>A batter's average after 16 innings is 36. How many runs are needed in the 17th innings to raise the average to 38?</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>has been</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>was</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>"Who" refers to "men", which is plural.</t>
+          <t>17 × 38 − 16 × 36 = 646 − 576 = 70.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Profit, Loss and Discount</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Choose the best version: [Walking down the road, the trees looked beautiful.]</t>
+          <t>Selling an article for ₹1,040 gives a loss of 20%. At what price should it be sold to gain 10%?</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>While walking down the road, the trees looked beautiful.</t>
+          <t>₹1,400</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Walking down the road, I found the trees beautiful.</t>
+          <t>₹1,430</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Walking down the road, the trees looked beautiful.</t>
+          <t>₹1,144</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The trees, walking down the road, looked beautiful.</t>
+          <t>₹1,300</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5700,473 +5643,475 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>The trees were not walking. The phrase must attach to the person walking.</t>
+          <t>Cost = 1,040 / 0.8 = 1,300. With 10% profit: 1,300 × 1.1 = ₹1,430.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Time and Work</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Had I known about the traffic, I ___ earlier.</t>
+          <t>A can do a job in 20 days and B in 30 days. They start together, but A leaves 5 days before the job is finished. How many days does the job take in all?</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>will leave</t>
+          <t>15 days</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>would have left</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>would leave</t>
+          <t>12 days</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>had left</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Past unreal condition: had + past participle, then would have + past participle.</t>
+          <t>If it takes T days: (T − 5)/20 + T/30 = 1, so 3T − 15 + 2T = 60 and T = 15.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Time, Speed and Distance</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>___ rich should help ___ poor.</t>
+          <t>A train passes a 240 m platform in 24 seconds and a person standing on the platform in 12 seconds. How long is the train?</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>A, a</t>
+          <t>360 m</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>The, the</t>
+          <t>120 m</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>No article, the</t>
+          <t>200 m</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>The, no article</t>
+          <t>240 m</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>"The" + adjective refers to a whole group of people.</t>
+          <t>L/12 = (L + 240)/24 gives 2L = L + 240, so L = 240 m.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Simple and Compound Interest</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Choose the correct sentence.</t>
+          <t>A sum doubles in 5 years at simple interest. In how many years will it become 4 times as much?</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>He is an university professor.</t>
+          <t>10 years</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>He is a university professor.</t>
+          <t>20 years</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>He is the university professor of a city.</t>
+          <t>12 years</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>He is university professor.</t>
+          <t>15 years</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>"University" starts with a "y" sound, so it takes "a".</t>
+          <t>Doubling means 100% interest in 5 years, so 20% a year. Four times needs 300%: 300 / 20 = 15 years.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Number System</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Which group of words can ALL be preceded by "a"?</t>
+          <t>What is the smallest number that leaves a remainder of 5 when divided by 6, by 8 and by 12?</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>umbrella, unicorn, union</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>hour, union, unit</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>unicorn, union, useful tool</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>apple, uniform, unit</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Umbrella, hour and apple start with vowel sounds.</t>
+          <t>LCM of 6, 8, 12 is 24. 24 + 5 = 29.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>___ Ramayana was written by Valmiki.</t>
+          <t>Production (tonnes):
+2021: 400 · 2022: 460 · 2023: 552
+Which year had the higher growth rate over the year before, and by how much?</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>Both years grew at the same rate</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2023, by 32 percentage points</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>2022, by 5 percentage points</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>No article</t>
+          <t>2023, by 5 percentage points</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Names of holy books take "the".</t>
+          <t>2022: 60/400 = 15%. 2023: 92/460 = 20%. 2023 is higher by 5 points.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Article Usage</t>
+          <t>Probability and P&amp;C</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Find the part with the error: My friend is / a engineer / at the / space agency.</t>
+          <t>A committee of 4 is chosen from 6 men and 4 women. What is the probability that it has exactly 2 women?</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>at the</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>My friend is</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>space agency</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>a engineer</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>"Engineer" starts with a vowel sound, so it takes "an".</t>
+          <t>C(6,2) × C(4,2) / C(10,4) = 15 × 6 / 210 = 3/7.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Number and Alphabet Series</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Trains of 150 m and 250 m run in the same direction at 72 km/h and 54 km/h. How long does the faster train take to pass the slower one?</t>
+          <t>AZ, CX, FU, JQ, ?</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>100 s</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>60 s</t>
+          <t>OL</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>80 s</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>40 s</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Relative speed 18 km/h = 5 m/s. Distance 400 m. 400/5 = 80 s.</t>
+          <t>First letters A, C, F, J go +2, +3, +4, +5 → O. Second letters Z, X, U, Q go −2, −3, −4, −5 → L.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Coding and Decoding</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>A car covers the first third of a distance at 20 km/h, the next third at 30 km/h and the last third at 60 km/h. What is the average speed?</t>
+          <t>If FRIEND is coded as HUMJTK, how is CANDLE coded?</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>36.7 km/h</t>
+          <t>DCQHQK</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>30 km/h</t>
+          <t>EDRIRM</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>33.3 km/h</t>
+          <t>ECRIRL</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>40 km/h</t>
+          <t>EDRIRL</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>3 / (1/20 + 1/30 + 1/60) = 3 / (6/60) = 30.</t>
+          <t>Letters move forward by 2, 3, 4, 5, 6, 7 in turn: C+2 = E, A+3 = D, N+4 = R, D+5 = I, L+6 = R, E+7 = L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Speed Time Distance</t>
+          <t>Blood Relations</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Two people start at the same time from A and B, 300 km apart, moving towards each other at 40 km/h and 60 km/h. After they meet, how long does the slower one take to reach B?</t>
+          <t>Introducing a man, Sunita says, "His wife is the only daughter of my father." How is the man related to Sunita?</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>4 h</t>
+          <t>Brother-in-law</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>4.5 h</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>5 h</t>
+          <t>Father-in-law</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>3 h</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -6177,155 +6122,155 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>They meet after 300/100 = 3 h. The slower one has 300 − 120 = 180 km left: 180/40 = 4.5 h.</t>
+          <t>The only daughter of Sunita's father is Sunita herself, so she is his wife.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>In how many ways can 5 men and 5 women sit around a round table so that men and women alternate?</t>
+          <t>Early in the morning, Asha's shadow falls exactly to her right. Which way is she facing?</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>South</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>North</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>East</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>West</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Men around the table: 4! = 24. Women in the 5 gaps: 5! = 120. 24 × 120 = 2880.</t>
+          <t>The morning sun is in the east, so the shadow points west. If west is on her right, she faces south.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Seating Arrangements</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>How many 4-digit even numbers can be formed from the digits 0–9 with no digit repeated?</t>
+          <t>Seven people A to G sit in a row facing north. D is in the middle. B is to the immediate left of D. A is at the left end and G at the right end. C is next to A. F sits between D and G, and E is not next to G. Who is to the immediate right of D?</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Ending in 0: 9 × 8 × 7 = 504. Ending in 2, 4, 6 or 8: 4 × 8 × 8 × 7 = 1792. Total 2296.</t>
+          <t>From the left: A, C, B, D, then E, F, G. E cannot be next to G, so E takes the seat by D.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Permutations and Combinations</t>
+          <t>Logical Puzzles</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>How many diagonals does a 12-sided polygon have?</t>
+          <t>Arun, Bala, Chitra and Divya each like a different game: cricket, football, tennis or chess. Arun likes neither cricket nor chess. Bala likes football. Chitra likes neither tennis nor cricket. Who likes cricket?</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Arun</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Chitra</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>Bala</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -6336,268 +6281,268 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>n(n − 3)/2 = 12 × 9 / 2 = 54.</t>
+          <t>Bala has football, so Arun has tennis and Chitra has chess. Cricket is left for Divya.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Mixtures and Alligations</t>
+          <t>Syllogisms</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>From 80 litres of pure milk, 8 litres are removed and replaced with water. This is done 3 times in all. How much milk is left?</t>
+          <t>Statements: Some doctors are writers. All writers are readers. No reader is lazy.
+Conclusion I: Some doctors are not lazy.
+Conclusion II: No writer is lazy.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>56 litres</t>
+          <t>Only I follows</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>59.04 litres</t>
+          <t>Only II follows</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>57.6 litres</t>
+          <t>Both follow</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>58.32 litres</t>
+          <t>Neither follows</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>80 × (1 − 8/80)³ = 80 × 0.729 = 58.32.</t>
+          <t>Writers are readers and no reader is lazy, so II follows. The doctors who are writers are therefore not lazy, so I follows too.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Ranking and Order</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>What is the probability that a leap year has 53 Sundays?</t>
+          <t>In a class of 40, Rohit is 9th from the top. Sana is 5 ranks below Rohit. What is Sana's rank from the bottom?</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>53/366</t>
+          <t>27th</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>31st</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>366 days = 52 weeks + 2 days. Of the 7 possible pairs of extra days, 2 include a Sunday.</t>
+          <t>Sana is 14th from the top. 40 − 14 + 1 = 27.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Data Sufficiency</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>An urn has 3 white and 2 black balls. All 5 are drawn one by one without replacement. What is the probability that the colours alternate?</t>
+          <t>What is the two-digit number N?
+(I) The digits of N add up to 7.
+(II) N is a prime number greater than 50.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>Only one of the statements alone is enough</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>Both statements together are needed, but neither alone</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>Cannot be answered even with both statements</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>Each statement alone is enough</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>It must go W B W B W: 3/5 × 2/4 × 2/3 × 1/2 × 1 = 1/10.</t>
+          <t>I allows 16, 25, 34, 43, 52, 61, 70; II allows many primes. Together only 61 fits.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Probability</t>
+          <t>Calendars and Clocks</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Three dice are thrown. What is the probability that all three show the same number?</t>
+          <t>At what time between 2 and 3 o'clock do the hour and minute hands overlap?</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10 10/11 minutes past 2</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>1/216</t>
+          <t>10 minutes past 2</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>12 8/11 minutes past 2</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>1/36</t>
+          <t>11 minutes past 2</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>6 favourable outcomes of 216: 6/216 = 1/36.</t>
+          <t>At 2:00 the gap is 60°. The minute hand gains 5.5° a minute: 60 / 5.5 = 10 10/11 minutes.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Subject-Verb Agreement</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>0, 6, 24, 60, 120, ?</t>
+          <t>Either the manager or the assistants ___ going to the meeting.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>are</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>was</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>has been</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -6605,113 +6550,105 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>n³ − n for n = 1 to 6.</t>
+          <t>With "either ... or", the verb agrees with the nearer subject, "assistants".</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Tenses</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2, 12, 36, 80, 150, ?</t>
+          <t>If he ___ harder, he would have passed.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>has worked</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>would work</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>had worked</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>worked</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>n³ + n² for n = 1 to 6.</t>
+          <t>Past unreal condition: if + had + past participle, then would have + past participle.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Error Spotting</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>4, 6, 12, 30, 90, ?</t>
+          <t>Find the part with the error: One of my friends / have gone / to Canada for higher studies.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>One of my friends</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>have gone</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>to Canada for higher studies</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>No error</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
           <t>B</t>
@@ -6719,396 +6656,383 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>× 1.5, × 2, × 2.5, × 3, × 3.5.</t>
+          <t>The subject is "one", so it takes "has gone".</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Sentence Correction</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>3, 8, 6, 15, 12, 24, 24, ?</t>
+          <t>Choose the correct sentence.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Unless you work hard, you will fail.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Unless you will work hard, you will fail.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>Unless you do not work hard, you will fail.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>If you do not work hard, unless you will fail.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Two series: 3, 6, 12, 24 (× 2) and 8, 15, 24, 35 (differences 7, 9, 11).</t>
+          <t>"Unless" already means "if not", so do not add another "not".</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Series Completion</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>7, 26, 63, 124, 215, ?</t>
+          <t>Passage: Many people believe multitasking saves time. However, studies of office workers show that switching between tasks can cut productivity by up to 40%, because the brain needs time to refocus each time. Those who group similar tasks together tend to finish sooner and make fewer errors.
+Which advice would the author most likely give?</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>Take on fewer tasks each day.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>Handle several tasks at once to save time.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>Work longer hours to make up for lost focus.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
+          <t>Finish one kind of task before moving to the next.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>n³ − 1 for n = 2 to 7 gives 342, which is not listed.</t>
+          <t>The passage praises grouping similar tasks to avoid the cost of switching.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Para Jumbles</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Is x² &gt; x?
-(I) x &gt; 1
-(II) x &lt; 0</t>
+          <t>Arrange the sentences in order:
+P: But the habit of reading for pleasure has declined.
+Q: Today, more books are published each year than ever before.
+R: Libraries are trying to reverse this with reading clubs.
+S: Many people say they no longer have the time or patience for long books.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>QPRS</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>QPSR</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>QSPR</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>PQSR</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Both ranges make x² &gt; x.</t>
+          <t>Fact (Q), contrast (P), reason (S), response (R).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Fill in the Blanks</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>What is the remainder when n is divided by 6?
-(I) n leaves remainder 2 when divided by 3.
-(II) n is odd.</t>
+          <t>The scientist's theory was at first ___, but later experiments proved it right.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>praised</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>adopted</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>dismissed</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>I allows remainder 2 or 5. Adding odd leaves only 5.</t>
+          <t>"But later ... proved it right" signals that it was first rejected.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Synonyms and Antonyms</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>What is the average age of a group of 5 people?
-(I) Their total age is 120 years.
-(II) The oldest is 40 and the youngest is 15.</t>
+          <t>Choose the word closest in meaning to METICULOUS.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Careless</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Painstaking</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Hasty</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Generous</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>I alone gives 24.</t>
+          <t>Meticulous means showing great attention to detail.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Articles and Prepositions</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Is the positive integer x prime?
-(I) x is even.
-(II) 1 &lt; x &lt; 4</t>
+          <t>Choose the correct sentence.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>An honesty is the best policy.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>The honesty is the best policy.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Honesty is the best policy.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Honesty is a best policy.</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>II gives 2 or 3, both prime. I allows 2 or 4.</t>
+          <t>Abstract nouns used in general take no article; superlatives take "the".</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>D2H</t>
+          <t>T2H</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Data Sufficiency</t>
+          <t>Critical Reasoning</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>What is the speed of the boat in still water?
-(I) It goes 24 km downstream in 2 hours.
-(II) It goes 24 km upstream in 4 hours.</t>
+          <t>Argument: "Students who eat breakfast score higher in exams. So eating breakfast improves exam scores." Which, if true, most weakens the conclusion?</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Only one of the statements alone is enough</t>
+          <t>Students who eat breakfast also tend to sleep more and study more regularly.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Both statements together are needed, but neither alone</t>
+          <t>Breakfast is the most important meal of the day.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Cannot be answered even with both statements</t>
+          <t>Some students skip breakfast to save time.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Each statement alone is enough</t>
+          <t>Exam scores have risen over the last five years.</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Down 12, up 6. Boat = (12 + 6)/2 = 9 km/h.</t>
+          <t>If breakfast-eaters also sleep and study more, those habits could explain the higher scores.</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7140,7 +7064,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tests sheet: one row per test. Test is a short code (e.g. D3R), Minutes is the time limit.</t>
+          <t>Tests sheet: one row per test. Test is a short code (e.g. T3R), Minutes is the time limit.</t>
         </is>
       </c>
     </row>
@@ -7188,6 +7112,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Changing a question changes how it shows in old attempts and the error log, so add new tests with new codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Save as .xlsx with the same name, then push to GitHub.</t>
         </is>
